--- a/written-exam-import.xlsx
+++ b/written-exam-import.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\MY_WORK\peter\qr-exams-system\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CFE682D-FFA7-48BA-A29A-62A42F36A69E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{997B6213-B62A-4F5B-85FE-B2B3AC4FEC32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="5">
   <si>
     <t>id</t>
   </si>
@@ -37,6 +37,9 @@
   </si>
   <si>
     <t>taks</t>
+  </si>
+  <si>
+    <t>coptic</t>
   </si>
 </sst>
 </file>
@@ -360,7 +363,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="10.21875" bestFit="1" customWidth="1"/>
@@ -381,90 +384,288 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2">
-        <v>24</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4">
-        <v>26</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>27</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C6">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C7">
-        <v>29</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C8">
-        <v>30</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>4</v>
+      </c>
+      <c r="C11">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C12">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C13">
         <v>20</v>
       </c>
-      <c r="B9" t="s">
-        <v>3</v>
-      </c>
-      <c r="C9">
-        <v>31</v>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>4</v>
+      </c>
+      <c r="C14">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>3</v>
+      </c>
+      <c r="C16">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>3</v>
+      </c>
+      <c r="C17">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>3</v>
+      </c>
+      <c r="C18">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>3</v>
+      </c>
+      <c r="C19">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>3</v>
+      </c>
+      <c r="C20">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>3</v>
+      </c>
+      <c r="C21">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>3</v>
+      </c>
+      <c r="C22">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>3</v>
+      </c>
+      <c r="C23">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>3</v>
+      </c>
+      <c r="C24">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>3</v>
+      </c>
+      <c r="C25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C26">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>3</v>
+      </c>
+      <c r="C27">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
